--- a/public/downloads/goldfin-13-week-cash-map-sample.xlsx
+++ b/public/downloads/goldfin-13-week-cash-map-sample.xlsx
@@ -18,8 +18,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0;[Red]($#,##0);-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; mo&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
   <fonts count="6">
@@ -189,7 +189,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -212,7 +212,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="8">
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="9">
@@ -232,7 +232,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="10">
@@ -242,7 +242,7 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="11">
@@ -313,7 +313,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 to 2026-05-31</t>
+          <t>2026-05-01 to 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -344,7 +344,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="7">
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>22881.25</v>
+        <v>22493.33</v>
       </c>
     </row>
     <row r="8">
@@ -364,7 +364,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>-18016.25</v>
+        <v>-16776.67</v>
       </c>
     </row>
     <row r="9">
@@ -374,7 +374,7 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <v>4865</v>
+        <v>5716.66</v>
       </c>
     </row>
     <row r="10">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <v>20400</v>
+        <v>218844</v>
       </c>
     </row>
     <row r="11">
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <v>43265</v>
+        <v>273716.66</v>
       </c>
     </row>
     <row r="13">
@@ -411,7 +411,7 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <v>48130</v>
+        <v>279433.32</v>
       </c>
     </row>
     <row r="14">
@@ -421,7 +421,7 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <v>52995</v>
+        <v>285149.98</v>
       </c>
     </row>
     <row r="15">
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <v>57860</v>
+        <v>290866.64</v>
       </c>
     </row>
     <row r="16">
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <v>62725</v>
+        <v>296583.3</v>
       </c>
     </row>
     <row r="17">
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B17" s="8">
-        <v>67590</v>
+        <v>302299.96</v>
       </c>
     </row>
     <row r="18">
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <v>72455</v>
+        <v>308016.62</v>
       </c>
     </row>
     <row r="19">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <v>77320</v>
+        <v>313733.28</v>
       </c>
     </row>
     <row r="20">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <v>82185</v>
+        <v>319449.94</v>
       </c>
     </row>
     <row r="21">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <v>87050</v>
+        <v>325166.6</v>
       </c>
     </row>
     <row r="22">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <v>91915</v>
+        <v>330883.26</v>
       </c>
     </row>
     <row r="23">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <v>96780</v>
+        <v>336599.92</v>
       </c>
     </row>
     <row r="24">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <v>101645</v>
+        <v>342316.58</v>
       </c>
     </row>
     <row r="25">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B25" s="11">
-        <v>5.6</v>
+        <v>3.67</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +661,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B4" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="5">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="6">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>41180</v>
+        <v>71900</v>
       </c>
     </row>
     <row r="7">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="8">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>6800</v>
+        <v>72948</v>
       </c>
     </row>
     <row r="9">
@@ -733,8 +733,8 @@
           <t>runwayMonths</t>
         </is>
       </c>
-      <c r="B9" s="8">
-        <v>5.6</v>
+      <c r="B9" s="11">
+        <v>3.67</v>
       </c>
     </row>
     <row r="10">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <v>14600</v>
+        <v>22700</v>
       </c>
     </row>
     <row r="11">
@@ -753,7 +753,7 @@
           <t>revenueVsPriorPct</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="10">
         <v>6.4</v>
       </c>
     </row>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="13">
@@ -773,7 +773,7 @@
           <t>profitVsPriorPct</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="10">
         <v>3.1</v>
       </c>
     </row>
@@ -793,7 +793,7 @@
           <t>coveragePct</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="10">
         <v>94</v>
       </c>
     </row>
@@ -803,7 +803,7 @@
           <t>transactionsCount</t>
         </is>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="12">
         <v>118</v>
       </c>
     </row>
@@ -813,7 +813,7 @@
           <t>reserve_floor_months</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="12">
         <v>3</v>
       </c>
     </row>
@@ -831,7 +831,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Detail</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Not embedded</t>
+          <t>Transaction detail</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>The current frontend report snapshot does not include raw transaction rows. Server-side XLSX generation can populate this sheet from the transactions table.</t>
+          <t>This planning workbook summarizes your connected bank and card activity. Line-item transaction detail lives in your GoldFin Desk account and your own bank export.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/goldfin-13-week-cash-map-sample.xlsx
+++ b/public/downloads/goldfin-13-week-cash-map-sample.xlsx
@@ -217,7 +217,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Sample figures</t>
+          <t>Sample figures (pre-filled - type over them)</t>
         </is>
       </c>
     </row>
@@ -251,16 +251,36 @@
         <v>71900</v>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Profit this month</t>
+        </is>
+      </c>
+      <c r="B14" s="8">
+        <v>24500</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Profit margin</t>
+        </is>
+      </c>
+      <c r="B15" s="10">
+        <v>25.41</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Prefer it filled from your bank every month? That is GoldFin Reports - goldfindesk.com/pricing</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>A planning artifact, not tax, accounting, credit, legal, or investment advice.</t>
         </is>
@@ -273,8 +293,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -330,190 +352,299 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Weekly money in</t>
+          <t>Cash floor to stay above</t>
         </is>
       </c>
       <c r="B8" s="14">
-        <v>22493</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Weekly money out</t>
-        </is>
-      </c>
-      <c r="B9" s="14">
-        <v>16777</v>
-      </c>
-    </row>
-    <row r="10"/>
+        <v>67000</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>13-week plan (edit any week's money in and out)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Results</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Money in</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Money out</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Ending cash</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Weekly net cash</t>
-        </is>
-      </c>
-      <c r="B12" s="9">
-        <f>$B$8-$B$9</f>
-        <v>5716</v>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B12" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C12" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D12" s="8">
+        <f>$B$7+B12-C12</f>
+        <v>273716</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>13-week cash path</t>
-        </is>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C13" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D13" s="8">
+        <f>D12+B13-C13</f>
+        <v>279432</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 1</t>
-        </is>
-      </c>
-      <c r="B14" s="8">
-        <f>$B$7+($B$8-$B$9)*1</f>
-        <v>273716</v>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C14" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D14" s="8">
+        <f>D13+B14-C14</f>
+        <v>285148</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 2</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>$B$7+($B$8-$B$9)*2</f>
-        <v>279432</v>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C15" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D15" s="8">
+        <f>D14+B15-C15</f>
+        <v>290864</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 3</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>$B$7+($B$8-$B$9)*3</f>
-        <v>285148</v>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="B16" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C16" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D16" s="8">
+        <f>D15+B16-C16</f>
+        <v>296580</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 4</t>
-        </is>
-      </c>
-      <c r="B17" s="8">
-        <f>$B$7+($B$8-$B$9)*4</f>
-        <v>290864</v>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="B17" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C17" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D17" s="8">
+        <f>D16+B17-C17</f>
+        <v>302296</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 5</t>
-        </is>
-      </c>
-      <c r="B18" s="8">
-        <f>$B$7+($B$8-$B$9)*5</f>
-        <v>296580</v>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="B18" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C18" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D18" s="8">
+        <f>D17+B18-C18</f>
+        <v>308012</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 6</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>$B$7+($B$8-$B$9)*6</f>
-        <v>302296</v>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="B19" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C19" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D19" s="8">
+        <f>D18+B19-C19</f>
+        <v>313728</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 7</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>$B$7+($B$8-$B$9)*7</f>
-        <v>308012</v>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="B20" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C20" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D20" s="8">
+        <f>D19+B20-C20</f>
+        <v>319444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 8</t>
-        </is>
-      </c>
-      <c r="B21" s="8">
-        <f>$B$7+($B$8-$B$9)*8</f>
-        <v>313728</v>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C21" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D21" s="8">
+        <f>D20+B21-C21</f>
+        <v>325160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 9</t>
-        </is>
-      </c>
-      <c r="B22" s="8">
-        <f>$B$7+($B$8-$B$9)*9</f>
-        <v>319444</v>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="B22" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C22" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D22" s="8">
+        <f>D21+B22-C22</f>
+        <v>330876</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 10</t>
-        </is>
-      </c>
-      <c r="B23" s="8">
-        <f>$B$7+($B$8-$B$9)*10</f>
-        <v>325160</v>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="B23" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C23" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D23" s="8">
+        <f>D22+B23-C23</f>
+        <v>336592</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 11</t>
-        </is>
-      </c>
-      <c r="B24" s="8">
-        <f>$B$7+($B$8-$B$9)*11</f>
-        <v>330876</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Projected cash - week 12</t>
-        </is>
-      </c>
-      <c r="B25" s="8">
-        <f>$B$7+($B$8-$B$9)*12</f>
-        <v>336592</v>
-      </c>
-    </row>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="B24" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C24" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D24" s="8">
+        <f>D23+B24-C24</f>
+        <v>342308</v>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Projected cash - week 13</t>
-        </is>
-      </c>
-      <c r="B26" s="8">
-        <f>$B$7+($B$8-$B$9)*13</f>
-        <v>342308</v>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Watch for the crunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Lowest weekly cash</t>
+        </is>
+      </c>
+      <c r="B27" s="8">
+        <f>MIN(D12:D24)</f>
+        <v>273716</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Weeks ending below your floor</t>
+        </is>
+      </c>
+      <c r="B28" s="12">
+        <f>COUNTIF(D12:D24,"&lt;"&amp;$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="13" t="str">
+        <f>IF(MIN(D12:D24)&lt;0,"Cash goes negative in this window - line up funding or slow outflows",IF(MIN(D12:D24)&lt;$B$8,"Cash dips below your floor - watch the tightest week","Cash stays above your floor across all 13 weeks"))</f>
+        <v>Cash stays above your floor across all 13 weeks</v>
       </c>
     </row>
   </sheetData>
